--- a/total_vente_trismestre.xlsx
+++ b/total_vente_trismestre.xlsx
@@ -345,13 +345,28 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:A1"/>
+  <dimension ref="A1:D1"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
       <c r="A1" t="inlineStr">
         <is>
-          <t>Article</t>
+          <t>Articles</t>
+        </is>
+      </c>
+      <c r="B1" t="inlineStr">
+        <is>
+          <t>Octobre</t>
+        </is>
+      </c>
+      <c r="C1" t="inlineStr">
+        <is>
+          <t>Novembre</t>
+        </is>
+      </c>
+      <c r="D1" t="inlineStr">
+        <is>
+          <t>Décembre</t>
         </is>
       </c>
     </row>

--- a/total_vente_trismestre.xlsx
+++ b/total_vente_trismestre.xlsx
@@ -345,7 +345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D1"/>
+  <dimension ref="A1:D5"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -367,6 +367,34 @@
       <c r="D1" t="inlineStr">
         <is>
           <t>Décembre</t>
+        </is>
+      </c>
+    </row>
+    <row r="2">
+      <c r="A2" t="inlineStr">
+        <is>
+          <t>Pommes</t>
+        </is>
+      </c>
+    </row>
+    <row r="3">
+      <c r="A3" t="inlineStr">
+        <is>
+          <t>dentifrice</t>
+        </is>
+      </c>
+    </row>
+    <row r="4">
+      <c r="A4" t="inlineStr">
+        <is>
+          <t>manga berserk</t>
+        </is>
+      </c>
+    </row>
+    <row r="5">
+      <c r="A5" t="inlineStr">
+        <is>
+          <t>Puce de téléphone</t>
         </is>
       </c>
     </row>

--- a/total_vente_trismestre.xlsx
+++ b/total_vente_trismestre.xlsx
@@ -380,21 +380,21 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>dentifrice</t>
+          <t>Poire</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>manga berserk</t>
+          <t>bannanemangue</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Puce de téléphone</t>
+          <t>Ananas</t>
         </is>
       </c>
     </row>

--- a/total_vente_trismestre.xlsx
+++ b/total_vente_trismestre.xlsx
@@ -387,14 +387,14 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bannanemangue</t>
+          <t>bannane</t>
         </is>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>Ananas</t>
+          <t>mangue</t>
         </is>
       </c>
     </row>

--- a/total_vente_trismestre.xlsx
+++ b/total_vente_trismestre.xlsx
@@ -345,7 +345,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:D5"/>
+  <dimension ref="A1:D6"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -376,26 +376,78 @@
           <t>Pommes</t>
         </is>
       </c>
+      <c r="B2" t="n">
+        <v>760</v>
+      </c>
+      <c r="C2" t="n">
+        <v>660</v>
+      </c>
+      <c r="D2" t="n">
+        <v>900</v>
+      </c>
     </row>
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>Poire</t>
-        </is>
+          <t>Poires</t>
+        </is>
+      </c>
+      <c r="B3" t="n">
+        <v>1050</v>
+      </c>
+      <c r="C3" t="n">
+        <v>625</v>
+      </c>
+      <c r="D3" t="n">
+        <v>594</v>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>bannane</t>
-        </is>
+          <t>Bananes</t>
+        </is>
+      </c>
+      <c r="B4" t="n">
+        <v>1250</v>
+      </c>
+      <c r="C4" t="n">
+        <v>1440</v>
+      </c>
+      <c r="D4" t="n">
+        <v>1170</v>
       </c>
     </row>
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>mangue</t>
-        </is>
+          <t>Mangues</t>
+        </is>
+      </c>
+      <c r="B5" t="n">
+        <v>900</v>
+      </c>
+      <c r="C5" t="n">
+        <v>1125</v>
+      </c>
+      <c r="D5" t="n">
+        <v>1254</v>
+      </c>
+    </row>
+    <row r="6">
+      <c r="A6" t="inlineStr">
+        <is>
+          <t>Ananas</t>
+        </is>
+      </c>
+      <c r="B6" t="n">
+        <v>950</v>
+      </c>
+      <c r="C6" t="n">
+        <v>880</v>
+      </c>
+      <c r="D6" t="n">
+        <v>756</v>
       </c>
     </row>
   </sheetData>

--- a/total_vente_trismestre.xlsx
+++ b/total_vente_trismestre.xlsx
@@ -54,6 +54,108 @@
   </cellStyles>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
 </styleSheet>
+</file>
+
+<file path=xl/charts/chart1.xml><?xml version="1.0" encoding="utf-8"?>
+<chartSpace xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns="http://schemas.openxmlformats.org/drawingml/2006/chart">
+  <chart>
+    <title>
+      <tx>
+        <rich>
+          <a:bodyPr/>
+          <a:p>
+            <a:pPr>
+              <a:defRPr/>
+            </a:pPr>
+            <a:r>
+              <a:t>Evolution du prix des pommes</a:t>
+            </a:r>
+          </a:p>
+        </rich>
+      </tx>
+    </title>
+    <plotArea>
+      <barChart>
+        <barDir val="col"/>
+        <grouping val="clustered"/>
+        <ser>
+          <idx val="0"/>
+          <order val="0"/>
+          <tx>
+            <v>Total vente en Euro</v>
+          </tx>
+          <spPr>
+            <a:ln>
+              <a:prstDash val="solid"/>
+            </a:ln>
+          </spPr>
+          <val>
+            <numRef>
+              <f>'Sheet'!$B$2:$D$2</f>
+            </numRef>
+          </val>
+        </ser>
+        <gapWidth val="150"/>
+        <axId val="10"/>
+        <axId val="100"/>
+      </barChart>
+      <catAx>
+        <axId val="10"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="100"/>
+        <lblOffset val="100"/>
+      </catAx>
+      <valAx>
+        <axId val="100"/>
+        <scaling>
+          <orientation val="minMax"/>
+        </scaling>
+        <axPos val="l"/>
+        <majorGridlines/>
+        <majorTickMark val="none"/>
+        <minorTickMark val="none"/>
+        <crossAx val="10"/>
+      </valAx>
+    </plotArea>
+    <legend>
+      <legendPos val="r"/>
+    </legend>
+    <plotVisOnly val="1"/>
+    <dispBlanksAs val="gap"/>
+  </chart>
+</chartSpace>
+</file>
+
+<file path=xl/drawings/drawing1.xml><?xml version="1.0" encoding="utf-8"?>
+<wsDr xmlns:a="http://schemas.openxmlformats.org/drawingml/2006/main" xmlns:c="http://schemas.openxmlformats.org/drawingml/2006/chart" xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/drawingml/2006/spreadsheetDrawing">
+  <oneCellAnchor>
+    <from>
+      <col>5</col>
+      <colOff>0</colOff>
+      <row>1</row>
+      <rowOff>0</rowOff>
+    </from>
+    <ext cx="5400000" cy="2700000"/>
+    <graphicFrame>
+      <nvGraphicFramePr>
+        <cNvPr id="1" name="Chart 1"/>
+        <cNvGraphicFramePr/>
+      </nvGraphicFramePr>
+      <xfrm/>
+      <a:graphic>
+        <a:graphicData uri="http://schemas.openxmlformats.org/drawingml/2006/chart">
+          <c:chart r:id="rId1"/>
+        </a:graphicData>
+      </a:graphic>
+    </graphicFrame>
+    <clientData/>
+  </oneCellAnchor>
+</wsDr>
 </file>
 
 <file path=xl/theme/theme1.xml><?xml version="1.0" encoding="utf-8"?>
@@ -452,5 +554,6 @@
     </row>
   </sheetData>
   <pageMargins left="0.75" right="0.75" top="1" bottom="1" header="0.5" footer="0.5"/>
+  <drawing xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" r:id="rId1"/>
 </worksheet>
 </file>